--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487656_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487656_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.1487</v>
+        <v>9.0021</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3687</v>
+        <v>4.2306</v>
       </c>
       <c r="F2" t="n">
-        <v>5.7799</v>
+        <v>4.7715</v>
       </c>
       <c r="G2" t="n">
         <v>6.696</v>
@@ -610,13 +610,13 @@
         <v>2.7164</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1692</v>
+        <v>1.0226</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8831</v>
+        <v>0.745</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2861</v>
+        <v>0.2777</v>
       </c>
       <c r="V2" t="n">
         <v>2.4477</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5492</v>
+        <v>6.3554</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6949</v>
+        <v>4.3376</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8543</v>
+        <v>2.0178</v>
       </c>
       <c r="G3" t="n">
         <v>4.1478</v>
@@ -688,13 +688,13 @@
         <v>1.9403</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5583</v>
+        <v>0.2479</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9691</v>
+        <v>-0.3264</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4107</v>
+        <v>0.5743</v>
       </c>
       <c r="V3" t="n">
         <v>0.9896</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.1155</v>
+        <v>4.6788</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4866</v>
+        <v>4.2679</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6289</v>
+        <v>0.4109</v>
       </c>
       <c r="G4" t="n">
         <v>5.867</v>
@@ -766,13 +766,13 @@
         <v>2.3284</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3381</v>
+        <v>-0.0987</v>
       </c>
       <c r="T4" t="n">
-        <v>0.305</v>
+        <v>0.0863</v>
       </c>
       <c r="U4" t="n">
-        <v>0.033</v>
+        <v>-0.185</v>
       </c>
       <c r="V4" t="n">
         <v>-2.4477</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. BERMEJO FAJARDO</t>
+          <t>L. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0624</v>
+        <v>0.5373</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3388</v>
+        <v>-0.5007</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4012</v>
+        <v>1.0379</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2493</v>
+        <v>3.129</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4111</v>
+        <v>1.0068</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1619</v>
+        <v>2.1222</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2165</v>
+        <v>2.9472</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0948</v>
+        <v>0.5191</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1218</v>
+        <v>2.4281</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0327</v>
+        <v>0.1818</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3164</v>
+        <v>0.4877</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2836</v>
+        <v>-0.3059</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5821</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5821</v>
+        <v>1.7463</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0002</v>
+        <v>-0.1559</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1222</v>
+        <v>-0.4896</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.122</v>
+        <v>0.3337</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.894</v>
+        <v>-1.2716</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.0478</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.894</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ SANCHEZ</t>
+          <t>D. PETIT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2238</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3435</v>
+        <v>-2.8398</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1197</v>
+        <v>2.9219</v>
       </c>
       <c r="G6" t="n">
-        <v>3.129</v>
+        <v>0.7328</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0068</v>
+        <v>0.304</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1222</v>
+        <v>0.4288</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9472</v>
+        <v>-0.3159</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5191</v>
+        <v>0.3007</v>
       </c>
       <c r="L6" t="n">
-        <v>2.4281</v>
+        <v>-0.6167</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1818</v>
+        <v>1.0487</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4877</v>
+        <v>0.0033</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3059</v>
+        <v>1.0454</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1642</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q6" t="n">
         <v>-2.9105</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7463</v>
+        <v>2.1344</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.917</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.3325</v>
+        <v>0.3866</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4155</v>
+        <v>-0.3089</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2716</v>
+        <v>0.0478</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0478</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2239</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. PETIT</t>
+          <t>F. BERMEJO FAJARDO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2569</v>
+        <v>0.022</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.0425</v>
+        <v>0.2597</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7856</v>
+        <v>-0.2377</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7328</v>
+        <v>0.2493</v>
       </c>
       <c r="H7" t="n">
-        <v>0.304</v>
+        <v>0.4111</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4288</v>
+        <v>-0.1619</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3159</v>
+        <v>0.2165</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3007</v>
+        <v>0.0948</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6167</v>
+        <v>0.1218</v>
       </c>
       <c r="M7" t="n">
-        <v>1.0487</v>
+        <v>0.0327</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0033</v>
+        <v>0.3164</v>
       </c>
       <c r="O7" t="n">
-        <v>1.0454</v>
+        <v>-0.2836</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7761</v>
+        <v>0.5821</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1344</v>
+        <v>0.5821</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2613</v>
+        <v>0.0847</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1839</v>
+        <v>0.0432</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4452</v>
+        <v>0.0415</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0478</v>
+        <v>-0.894</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0478</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. BUHORSKYI</t>
+          <t>P. VILLANUEVA LAZARO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2617</v>
+        <v>-0.5855</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7411</v>
+        <v>-2.7551</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5206</v>
+        <v>2.1696</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4008</v>
+        <v>0.8238</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2776</v>
+        <v>1.1897</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6785</v>
+        <v>-0.3659</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3501</v>
+        <v>0.242</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3501</v>
+        <v>0.9804</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.7385</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.751</v>
+        <v>0.5818</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0725</v>
+        <v>0.2092</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6785</v>
+        <v>0.3725</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7761</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R8" t="n">
-        <v>0.194</v>
+        <v>1.9403</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0848</v>
+        <v>-0.8168</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1211</v>
+        <v>-0.0867</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0363</v>
+        <v>-0.7301</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3776</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.3776</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7308</v>
+        <v>-1.0518</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.748</v>
+        <v>-1.2871</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0172</v>
+        <v>0.2353</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2296</v>
@@ -1156,13 +1156,13 @@
         <v>0.9702</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5774</v>
+        <v>-0.8984</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.424</v>
+        <v>0.037</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1534</v>
+        <v>-0.9354</v>
       </c>
       <c r="V9" t="n">
         <v>-0.894</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. VILLANUEVA LAZARO</t>
+          <t>D. BUHORSKYI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0736</v>
+        <v>-1.2072</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6981</v>
+        <v>-0.7411</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6245</v>
+        <v>-0.4661</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8238</v>
+        <v>-0.4008</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1897</v>
+        <v>0.2776</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3659</v>
+        <v>-0.6785</v>
       </c>
       <c r="J10" t="n">
-        <v>0.242</v>
+        <v>0.3501</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9804</v>
+        <v>0.3501</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7385</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5818</v>
+        <v>-0.751</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2092</v>
+        <v>-0.0725</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3725</v>
+        <v>-0.6785</v>
       </c>
       <c r="P10" t="n">
+        <v>-0.7761</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-0.9702</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-2.9105</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.9403</v>
+        <v>0.194</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.3048</v>
+        <v>-0.0303</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0296</v>
+        <v>-0.1211</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.2752</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3776</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3776</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1277</v>
+        <v>-1.9398</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0615</v>
+        <v>-1.9008</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0663</v>
+        <v>-0.039</v>
       </c>
       <c r="G11" t="n">
         <v>-0.0115</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1759</v>
+        <v>0.0121</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1211</v>
+        <v>0.0395</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0547</v>
+        <v>-0.0275</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>14.0765</v>
+        <v>15.8934</v>
       </c>
       <c r="E12" t="n">
-        <v>1.254299999999999</v>
+        <v>3.071199999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>12.822</v>
+        <v>12.8221</v>
       </c>
       <c r="G12" t="n">
         <v>21.0038</v>
@@ -1360,7 +1360,7 @@
         <v>13.635</v>
       </c>
       <c r="I12" t="n">
-        <v>7.368399999999999</v>
+        <v>7.368400000000001</v>
       </c>
       <c r="J12" t="n">
         <v>16.5963</v>
@@ -1369,7 +1369,7 @@
         <v>11.007</v>
       </c>
       <c r="L12" t="n">
-        <v>5.589099999999998</v>
+        <v>5.589099999999999</v>
       </c>
       <c r="M12" t="n">
         <v>4.4072</v>
@@ -1390,13 +1390,13 @@
         <v>14.5524</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.372</v>
+        <v>-0.5550999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.5032</v>
+        <v>0.3138</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8688999999999998</v>
+        <v>-0.8688999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-1.6446</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5168</v>
+        <v>1.8349</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3992</v>
+        <v>0.4993</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1176</v>
+        <v>1.3356</v>
       </c>
       <c r="G13" t="n">
         <v>-0.1939</v>
@@ -1468,13 +1468,13 @@
         <v>1.1642</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3405</v>
+        <v>0.6586</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2075</v>
+        <v>0.3076</v>
       </c>
       <c r="U13" t="n">
-        <v>0.133</v>
+        <v>0.3511</v>
       </c>
       <c r="V13" t="n">
         <v>1.1761</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3943</v>
+        <v>1.2947</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.0549</v>
+        <v>-0.8547</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4492</v>
+        <v>2.1494</v>
       </c>
       <c r="G14" t="n">
         <v>1.8029</v>
@@ -1546,13 +1546,13 @@
         <v>2.7164</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1153</v>
+        <v>0.0157</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7134</v>
+        <v>-0.5132</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8287</v>
+        <v>0.5289</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3299</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6741</v>
+        <v>0.7564</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7076</v>
+        <v>-0.4073</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3817</v>
+        <v>1.1636</v>
       </c>
       <c r="G15" t="n">
         <v>0.2015</v>
@@ -1624,13 +1624,13 @@
         <v>1.7463</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3035</v>
+        <v>-0.2212</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0173</v>
+        <v>-0.717</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7138</v>
+        <v>0.4958</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. GARCIA-LARRACHE SEGURA</t>
+          <t>E. PASCUAL COZAR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3068</v>
+        <v>-0.4469</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0365</v>
+        <v>0.5221</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2703</v>
+        <v>-0.969</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5628</v>
+        <v>-1.4303</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0412</v>
+        <v>-2.6076</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5217000000000001</v>
+        <v>1.1773</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7295</v>
+        <v>1.0871</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6838</v>
+        <v>-0.2348</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0456</v>
+        <v>1.3219</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2923</v>
+        <v>-2.5174</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.725</v>
+        <v>-2.3728</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5673</v>
+        <v>-0.1446</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5821</v>
+        <v>0.7761</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5523</v>
+        <v>1.7463</v>
       </c>
       <c r="S16" t="n">
-        <v>0.995</v>
+        <v>0.2072</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9847</v>
+        <v>0.4051</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0104</v>
+        <v>-0.1979</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.7075</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.7075</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. HERMOSO ALCUBILLA</t>
+          <t>J. GARCIA-LARRACHE SEGURA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4692</v>
+        <v>-0.5029</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8794</v>
+        <v>-0.6642</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4102</v>
+        <v>0.1613</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.822</v>
+        <v>-0.5628</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.8127</v>
+        <v>-0.0412</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0093</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>-3.2257</v>
+        <v>0.7295</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.6446</v>
+        <v>0.6838</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5810999999999999</v>
+        <v>0.0456</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5963000000000001</v>
+        <v>-1.2923</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1681</v>
+        <v>-0.725</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4282</v>
+        <v>-0.5673</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9702</v>
+        <v>0.5821</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9403</v>
+        <v>1.5523</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.1853</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2568</v>
+        <v>0.284</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2901</v>
+        <v>-0.0987</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8358</v>
+        <v>-0.7075</v>
       </c>
       <c r="W17" t="n">
-        <v>3.0597</v>
+        <v>-0.7075</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. GARCIA LARRACHE SEGURA</t>
+          <t>M. HERMOSO ALCUBILLA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1898</v>
+        <v>-0.5515</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9758</v>
+        <v>-1.1797</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.214</v>
+        <v>0.6282</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1425</v>
+        <v>-3.822</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7852</v>
+        <v>-2.8127</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9276</v>
+        <v>-1.0093</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6594</v>
+        <v>-3.2257</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6138</v>
+        <v>-2.6446</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0456</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8018999999999999</v>
+        <v>-0.5963000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1714</v>
+        <v>-0.1681</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9733000000000001</v>
+        <v>-0.4282</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7761</v>
+        <v>0.9702</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7463</v>
+        <v>1.9403</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5996</v>
+        <v>0.4646</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6651</v>
+        <v>-0.0435</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0655</v>
+        <v>0.5081</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2239</v>
+        <v>1.8358</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.0597</v>
       </c>
       <c r="X18" t="n">
         <v>-1.2239</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. PASCUAL COZAR</t>
+          <t>L. GARCIA LARRACHE SEGURA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5931</v>
+        <v>-0.8989</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3788</v>
+        <v>-0.8757</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2143</v>
+        <v>-0.0232</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4303</v>
+        <v>-0.1425</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.6076</v>
+        <v>0.7852</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1773</v>
+        <v>-0.9276</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0871</v>
+        <v>0.6594</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2348</v>
+        <v>0.6138</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3219</v>
+        <v>0.0456</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.5174</v>
+        <v>-0.8018999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.3728</v>
+        <v>0.1714</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1446</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="P19" t="n">
         <v>0.7761</v>
@@ -1936,22 +1936,22 @@
         <v>1.7463</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9389999999999999</v>
+        <v>-0.3087</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4958</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4432</v>
+        <v>0.2563</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.3785</v>
+        <v>-4.3146</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.098</v>
+        <v>-2.8978</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2804</v>
+        <v>-1.4167</v>
       </c>
       <c r="G20" t="n">
         <v>-7.1553</v>
@@ -2014,13 +2014,13 @@
         <v>2.1344</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7469</v>
+        <v>0.8109</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4149</v>
+        <v>0.6151</v>
       </c>
       <c r="U20" t="n">
-        <v>0.332</v>
+        <v>0.1957</v>
       </c>
       <c r="V20" t="n">
         <v>1.8358</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. MANZANERO CAMACHO</t>
+          <t>N. LASUNCION MARIBLANCA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.5214</v>
+        <v>-5.2524</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0648</v>
+        <v>-2.6981</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4565</v>
+        <v>-2.5543</v>
       </c>
       <c r="G21" t="n">
-        <v>-7.1784</v>
+        <v>-2.5228</v>
       </c>
       <c r="H21" t="n">
-        <v>-6.3776</v>
+        <v>-1.5769</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8008</v>
+        <v>-0.9459</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.8319</v>
+        <v>-0.6293</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.8598</v>
+        <v>0.033</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0279</v>
+        <v>-0.6623</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.3464</v>
+        <v>-1.8935</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.5178</v>
+        <v>-1.6099</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8286</v>
+        <v>-0.2836</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7761</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7463</v>
+        <v>0.9702</v>
       </c>
       <c r="S21" t="n">
-        <v>1.8809</v>
+        <v>0.1525</v>
       </c>
       <c r="T21" t="n">
-        <v>1.7373</v>
+        <v>0.5596</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1436</v>
+        <v>-0.4071</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.9418</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. LASUNCION MARIBLANCA</t>
+          <t>D. MANZANERO CAMACHO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.8164</v>
+        <v>-5.9951</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0985</v>
+        <v>-4.266</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.7179</v>
+        <v>-1.7291</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5228</v>
+        <v>-7.1784</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.5769</v>
+        <v>-6.3776</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9459</v>
+        <v>-0.8008</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6293</v>
+        <v>-3.8319</v>
       </c>
       <c r="K22" t="n">
-        <v>0.033</v>
+        <v>-3.8598</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6623</v>
+        <v>0.0279</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8935</v>
+        <v>-3.3464</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.6099</v>
+        <v>-2.5178</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2836</v>
+        <v>-0.8286</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.9403</v>
+        <v>0.7761</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9702</v>
+        <v>1.7463</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4114</v>
+        <v>0.4071</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1592</v>
+        <v>0.5361</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5706</v>
+        <v>-0.129</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9418</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-14.0764</v>
+        <v>-14.0763</v>
       </c>
       <c r="E23" t="n">
         <v>-12.8221</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2541</v>
+        <v>-1.254200000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-21.0036</v>
@@ -2221,13 +2221,13 @@
         <v>-7.3684</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.407100000000001</v>
+        <v>-4.4071</v>
       </c>
       <c r="K23" t="n">
         <v>-2.628000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.779199999999999</v>
+        <v>-1.7792</v>
       </c>
       <c r="M23" t="n">
         <v>-16.5963</v>
@@ -2239,7 +2239,7 @@
         <v>-5.5892</v>
       </c>
       <c r="P23" t="n">
-        <v>2.9104</v>
+        <v>2.910400000000001</v>
       </c>
       <c r="Q23" t="n">
         <v>-14.5527</v>
@@ -2251,16 +2251,16 @@
         <v>2.372</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8687999999999998</v>
+        <v>0.8688</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5033</v>
+        <v>1.5032</v>
       </c>
       <c r="V23" t="n">
         <v>1.6446</v>
       </c>
       <c r="W23" t="n">
-        <v>5.2686</v>
+        <v>5.268599999999999</v>
       </c>
       <c r="X23" t="n">
         <v>-3.6239</v>
